--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_04-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_04-10-2025.xlsx
@@ -592,25 +592,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff79ce41eb5+80197]
-	GetHandleVerifier [0x0x7ff79ce41f10+80288]
-	(No symbol) [0x0x7ff79cbc02fa]
-	(No symbol) [0x0x7ff79cc17cd7]
-	(No symbol) [0x0x7ff79cc17f9c]
-	(No symbol) [0x0x7ff79cc6ba87]
-	(No symbol) [0x0x7ff79cc403bf]
-	(No symbol) [0x0x7ff79cc687fb]
-	(No symbol) [0x0x7ff79cc40153]
-	(No symbol) [0x0x7ff79cc08b02]
-	(No symbol) [0x0x7ff79cc098d3]
-	GetHandleVerifier [0x0x7ff79d0fe83d+2949837]
-	GetHandleVerifier [0x0x7ff79d0f8c6a+2926330]
-	GetHandleVerifier [0x0x7ff79d1186c7+3055959]
-	GetHandleVerifier [0x0x7ff79ce5cfee+191102]
-	GetHandleVerifier [0x0x7ff79ce650af+224063]
-	GetHandleVerifier [0x0x7ff79ce4af64+117236]
-	GetHandleVerifier [0x0x7ff79ce4b119+117673]
-	GetHandleVerifier [0x0x7ff79ce310a8+11064]
+	GetHandleVerifier [0x0x7ff716ef1eb5+80197]
+	GetHandleVerifier [0x0x7ff716ef1f10+80288]
+	(No symbol) [0x0x7ff716c702fa]
+	(No symbol) [0x0x7ff716cc7cd7]
+	(No symbol) [0x0x7ff716cc7f9c]
+	(No symbol) [0x0x7ff716d1ba87]
+	(No symbol) [0x0x7ff716cf03bf]
+	(No symbol) [0x0x7ff716d187fb]
+	(No symbol) [0x0x7ff716cf0153]
+	(No symbol) [0x0x7ff716cb8b02]
+	(No symbol) [0x0x7ff716cb98d3]
+	GetHandleVerifier [0x0x7ff7171ae83d+2949837]
+	GetHandleVerifier [0x0x7ff7171a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7171c86c7+3055959]
+	GetHandleVerifier [0x0x7ff716f0cfee+191102]
+	GetHandleVerifier [0x0x7ff716f150af+224063]
+	GetHandleVerifier [0x0x7ff716efaf64+117236]
+	GetHandleVerifier [0x0x7ff716efb119+117673]
+	GetHandleVerifier [0x0x7ff716ee10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -714,25 +714,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff79ce41eb5+80197]
-	GetHandleVerifier [0x0x7ff79ce41f10+80288]
-	(No symbol) [0x0x7ff79cbc02fa]
-	(No symbol) [0x0x7ff79cc17cd7]
-	(No symbol) [0x0x7ff79cc17f9c]
-	(No symbol) [0x0x7ff79cc6ba87]
-	(No symbol) [0x0x7ff79cc403bf]
-	(No symbol) [0x0x7ff79cc687fb]
-	(No symbol) [0x0x7ff79cc40153]
-	(No symbol) [0x0x7ff79cc08b02]
-	(No symbol) [0x0x7ff79cc098d3]
-	GetHandleVerifier [0x0x7ff79d0fe83d+2949837]
-	GetHandleVerifier [0x0x7ff79d0f8c6a+2926330]
-	GetHandleVerifier [0x0x7ff79d1186c7+3055959]
-	GetHandleVerifier [0x0x7ff79ce5cfee+191102]
-	GetHandleVerifier [0x0x7ff79ce650af+224063]
-	GetHandleVerifier [0x0x7ff79ce4af64+117236]
-	GetHandleVerifier [0x0x7ff79ce4b119+117673]
-	GetHandleVerifier [0x0x7ff79ce310a8+11064]
+	GetHandleVerifier [0x0x7ff716ef1eb5+80197]
+	GetHandleVerifier [0x0x7ff716ef1f10+80288]
+	(No symbol) [0x0x7ff716c702fa]
+	(No symbol) [0x0x7ff716cc7cd7]
+	(No symbol) [0x0x7ff716cc7f9c]
+	(No symbol) [0x0x7ff716d1ba87]
+	(No symbol) [0x0x7ff716cf03bf]
+	(No symbol) [0x0x7ff716d187fb]
+	(No symbol) [0x0x7ff716cf0153]
+	(No symbol) [0x0x7ff716cb8b02]
+	(No symbol) [0x0x7ff716cb98d3]
+	GetHandleVerifier [0x0x7ff7171ae83d+2949837]
+	GetHandleVerifier [0x0x7ff7171a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7171c86c7+3055959]
+	GetHandleVerifier [0x0x7ff716f0cfee+191102]
+	GetHandleVerifier [0x0x7ff716f150af+224063]
+	GetHandleVerifier [0x0x7ff716efaf64+117236]
+	GetHandleVerifier [0x0x7ff716efb119+117673]
+	GetHandleVerifier [0x0x7ff716ee10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -836,25 +836,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff79ce41eb5+80197]
-	GetHandleVerifier [0x0x7ff79ce41f10+80288]
-	(No symbol) [0x0x7ff79cbc02fa]
-	(No symbol) [0x0x7ff79cc17cd7]
-	(No symbol) [0x0x7ff79cc17f9c]
-	(No symbol) [0x0x7ff79cc6ba87]
-	(No symbol) [0x0x7ff79cc403bf]
-	(No symbol) [0x0x7ff79cc687fb]
-	(No symbol) [0x0x7ff79cc40153]
-	(No symbol) [0x0x7ff79cc08b02]
-	(No symbol) [0x0x7ff79cc098d3]
-	GetHandleVerifier [0x0x7ff79d0fe83d+2949837]
-	GetHandleVerifier [0x0x7ff79d0f8c6a+2926330]
-	GetHandleVerifier [0x0x7ff79d1186c7+3055959]
-	GetHandleVerifier [0x0x7ff79ce5cfee+191102]
-	GetHandleVerifier [0x0x7ff79ce650af+224063]
-	GetHandleVerifier [0x0x7ff79ce4af64+117236]
-	GetHandleVerifier [0x0x7ff79ce4b119+117673]
-	GetHandleVerifier [0x0x7ff79ce310a8+11064]
+	GetHandleVerifier [0x0x7ff716ef1eb5+80197]
+	GetHandleVerifier [0x0x7ff716ef1f10+80288]
+	(No symbol) [0x0x7ff716c702fa]
+	(No symbol) [0x0x7ff716cc7cd7]
+	(No symbol) [0x0x7ff716cc7f9c]
+	(No symbol) [0x0x7ff716d1ba87]
+	(No symbol) [0x0x7ff716cf03bf]
+	(No symbol) [0x0x7ff716d187fb]
+	(No symbol) [0x0x7ff716cf0153]
+	(No symbol) [0x0x7ff716cb8b02]
+	(No symbol) [0x0x7ff716cb98d3]
+	GetHandleVerifier [0x0x7ff7171ae83d+2949837]
+	GetHandleVerifier [0x0x7ff7171a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7171c86c7+3055959]
+	GetHandleVerifier [0x0x7ff716f0cfee+191102]
+	GetHandleVerifier [0x0x7ff716f150af+224063]
+	GetHandleVerifier [0x0x7ff716efaf64+117236]
+	GetHandleVerifier [0x0x7ff716efb119+117673]
+	GetHandleVerifier [0x0x7ff716ee10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -958,25 +958,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff79ce41eb5+80197]
-	GetHandleVerifier [0x0x7ff79ce41f10+80288]
-	(No symbol) [0x0x7ff79cbc02fa]
-	(No symbol) [0x0x7ff79cc17cd7]
-	(No symbol) [0x0x7ff79cc17f9c]
-	(No symbol) [0x0x7ff79cc6ba87]
-	(No symbol) [0x0x7ff79cc403bf]
-	(No symbol) [0x0x7ff79cc687fb]
-	(No symbol) [0x0x7ff79cc40153]
-	(No symbol) [0x0x7ff79cc08b02]
-	(No symbol) [0x0x7ff79cc098d3]
-	GetHandleVerifier [0x0x7ff79d0fe83d+2949837]
-	GetHandleVerifier [0x0x7ff79d0f8c6a+2926330]
-	GetHandleVerifier [0x0x7ff79d1186c7+3055959]
-	GetHandleVerifier [0x0x7ff79ce5cfee+191102]
-	GetHandleVerifier [0x0x7ff79ce650af+224063]
-	GetHandleVerifier [0x0x7ff79ce4af64+117236]
-	GetHandleVerifier [0x0x7ff79ce4b119+117673]
-	GetHandleVerifier [0x0x7ff79ce310a8+11064]
+	GetHandleVerifier [0x0x7ff716ef1eb5+80197]
+	GetHandleVerifier [0x0x7ff716ef1f10+80288]
+	(No symbol) [0x0x7ff716c702fa]
+	(No symbol) [0x0x7ff716cc7cd7]
+	(No symbol) [0x0x7ff716cc7f9c]
+	(No symbol) [0x0x7ff716d1ba87]
+	(No symbol) [0x0x7ff716cf03bf]
+	(No symbol) [0x0x7ff716d187fb]
+	(No symbol) [0x0x7ff716cf0153]
+	(No symbol) [0x0x7ff716cb8b02]
+	(No symbol) [0x0x7ff716cb98d3]
+	GetHandleVerifier [0x0x7ff7171ae83d+2949837]
+	GetHandleVerifier [0x0x7ff7171a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7171c86c7+3055959]
+	GetHandleVerifier [0x0x7ff716f0cfee+191102]
+	GetHandleVerifier [0x0x7ff716f150af+224063]
+	GetHandleVerifier [0x0x7ff716efaf64+117236]
+	GetHandleVerifier [0x0x7ff716efb119+117673]
+	GetHandleVerifier [0x0x7ff716ee10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1080,25 +1080,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff79ce41eb5+80197]
-	GetHandleVerifier [0x0x7ff79ce41f10+80288]
-	(No symbol) [0x0x7ff79cbc02fa]
-	(No symbol) [0x0x7ff79cc17cd7]
-	(No symbol) [0x0x7ff79cc17f9c]
-	(No symbol) [0x0x7ff79cc6ba87]
-	(No symbol) [0x0x7ff79cc403bf]
-	(No symbol) [0x0x7ff79cc687fb]
-	(No symbol) [0x0x7ff79cc40153]
-	(No symbol) [0x0x7ff79cc08b02]
-	(No symbol) [0x0x7ff79cc098d3]
-	GetHandleVerifier [0x0x7ff79d0fe83d+2949837]
-	GetHandleVerifier [0x0x7ff79d0f8c6a+2926330]
-	GetHandleVerifier [0x0x7ff79d1186c7+3055959]
-	GetHandleVerifier [0x0x7ff79ce5cfee+191102]
-	GetHandleVerifier [0x0x7ff79ce650af+224063]
-	GetHandleVerifier [0x0x7ff79ce4af64+117236]
-	GetHandleVerifier [0x0x7ff79ce4b119+117673]
-	GetHandleVerifier [0x0x7ff79ce310a8+11064]
+	GetHandleVerifier [0x0x7ff716ef1eb5+80197]
+	GetHandleVerifier [0x0x7ff716ef1f10+80288]
+	(No symbol) [0x0x7ff716c702fa]
+	(No symbol) [0x0x7ff716cc7cd7]
+	(No symbol) [0x0x7ff716cc7f9c]
+	(No symbol) [0x0x7ff716d1ba87]
+	(No symbol) [0x0x7ff716cf03bf]
+	(No symbol) [0x0x7ff716d187fb]
+	(No symbol) [0x0x7ff716cf0153]
+	(No symbol) [0x0x7ff716cb8b02]
+	(No symbol) [0x0x7ff716cb98d3]
+	GetHandleVerifier [0x0x7ff7171ae83d+2949837]
+	GetHandleVerifier [0x0x7ff7171a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7171c86c7+3055959]
+	GetHandleVerifier [0x0x7ff716f0cfee+191102]
+	GetHandleVerifier [0x0x7ff716f150af+224063]
+	GetHandleVerifier [0x0x7ff716efaf64+117236]
+	GetHandleVerifier [0x0x7ff716efb119+117673]
+	GetHandleVerifier [0x0x7ff716ee10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1202,25 +1202,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff79ce41eb5+80197]
-	GetHandleVerifier [0x0x7ff79ce41f10+80288]
-	(No symbol) [0x0x7ff79cbc02fa]
-	(No symbol) [0x0x7ff79cc17cd7]
-	(No symbol) [0x0x7ff79cc17f9c]
-	(No symbol) [0x0x7ff79cc6ba87]
-	(No symbol) [0x0x7ff79cc403bf]
-	(No symbol) [0x0x7ff79cc687fb]
-	(No symbol) [0x0x7ff79cc40153]
-	(No symbol) [0x0x7ff79cc08b02]
-	(No symbol) [0x0x7ff79cc098d3]
-	GetHandleVerifier [0x0x7ff79d0fe83d+2949837]
-	GetHandleVerifier [0x0x7ff79d0f8c6a+2926330]
-	GetHandleVerifier [0x0x7ff79d1186c7+3055959]
-	GetHandleVerifier [0x0x7ff79ce5cfee+191102]
-	GetHandleVerifier [0x0x7ff79ce650af+224063]
-	GetHandleVerifier [0x0x7ff79ce4af64+117236]
-	GetHandleVerifier [0x0x7ff79ce4b119+117673]
-	GetHandleVerifier [0x0x7ff79ce310a8+11064]
+	GetHandleVerifier [0x0x7ff716ef1eb5+80197]
+	GetHandleVerifier [0x0x7ff716ef1f10+80288]
+	(No symbol) [0x0x7ff716c702fa]
+	(No symbol) [0x0x7ff716cc7cd7]
+	(No symbol) [0x0x7ff716cc7f9c]
+	(No symbol) [0x0x7ff716d1ba87]
+	(No symbol) [0x0x7ff716cf03bf]
+	(No symbol) [0x0x7ff716d187fb]
+	(No symbol) [0x0x7ff716cf0153]
+	(No symbol) [0x0x7ff716cb8b02]
+	(No symbol) [0x0x7ff716cb98d3]
+	GetHandleVerifier [0x0x7ff7171ae83d+2949837]
+	GetHandleVerifier [0x0x7ff7171a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7171c86c7+3055959]
+	GetHandleVerifier [0x0x7ff716f0cfee+191102]
+	GetHandleVerifier [0x0x7ff716f150af+224063]
+	GetHandleVerifier [0x0x7ff716efaf64+117236]
+	GetHandleVerifier [0x0x7ff716efb119+117673]
+	GetHandleVerifier [0x0x7ff716ee10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1324,25 +1324,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff79ce41eb5+80197]
-	GetHandleVerifier [0x0x7ff79ce41f10+80288]
-	(No symbol) [0x0x7ff79cbc02fa]
-	(No symbol) [0x0x7ff79cc17cd7]
-	(No symbol) [0x0x7ff79cc17f9c]
-	(No symbol) [0x0x7ff79cc6ba87]
-	(No symbol) [0x0x7ff79cc403bf]
-	(No symbol) [0x0x7ff79cc687fb]
-	(No symbol) [0x0x7ff79cc40153]
-	(No symbol) [0x0x7ff79cc08b02]
-	(No symbol) [0x0x7ff79cc098d3]
-	GetHandleVerifier [0x0x7ff79d0fe83d+2949837]
-	GetHandleVerifier [0x0x7ff79d0f8c6a+2926330]
-	GetHandleVerifier [0x0x7ff79d1186c7+3055959]
-	GetHandleVerifier [0x0x7ff79ce5cfee+191102]
-	GetHandleVerifier [0x0x7ff79ce650af+224063]
-	GetHandleVerifier [0x0x7ff79ce4af64+117236]
-	GetHandleVerifier [0x0x7ff79ce4b119+117673]
-	GetHandleVerifier [0x0x7ff79ce310a8+11064]
+	GetHandleVerifier [0x0x7ff716ef1eb5+80197]
+	GetHandleVerifier [0x0x7ff716ef1f10+80288]
+	(No symbol) [0x0x7ff716c702fa]
+	(No symbol) [0x0x7ff716cc7cd7]
+	(No symbol) [0x0x7ff716cc7f9c]
+	(No symbol) [0x0x7ff716d1ba87]
+	(No symbol) [0x0x7ff716cf03bf]
+	(No symbol) [0x0x7ff716d187fb]
+	(No symbol) [0x0x7ff716cf0153]
+	(No symbol) [0x0x7ff716cb8b02]
+	(No symbol) [0x0x7ff716cb98d3]
+	GetHandleVerifier [0x0x7ff7171ae83d+2949837]
+	GetHandleVerifier [0x0x7ff7171a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7171c86c7+3055959]
+	GetHandleVerifier [0x0x7ff716f0cfee+191102]
+	GetHandleVerifier [0x0x7ff716f150af+224063]
+	GetHandleVerifier [0x0x7ff716efaf64+117236]
+	GetHandleVerifier [0x0x7ff716efb119+117673]
+	GetHandleVerifier [0x0x7ff716ee10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1446,25 +1446,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff79ce41eb5+80197]
-	GetHandleVerifier [0x0x7ff79ce41f10+80288]
-	(No symbol) [0x0x7ff79cbc02fa]
-	(No symbol) [0x0x7ff79cc17cd7]
-	(No symbol) [0x0x7ff79cc17f9c]
-	(No symbol) [0x0x7ff79cc6ba87]
-	(No symbol) [0x0x7ff79cc403bf]
-	(No symbol) [0x0x7ff79cc687fb]
-	(No symbol) [0x0x7ff79cc40153]
-	(No symbol) [0x0x7ff79cc08b02]
-	(No symbol) [0x0x7ff79cc098d3]
-	GetHandleVerifier [0x0x7ff79d0fe83d+2949837]
-	GetHandleVerifier [0x0x7ff79d0f8c6a+2926330]
-	GetHandleVerifier [0x0x7ff79d1186c7+3055959]
-	GetHandleVerifier [0x0x7ff79ce5cfee+191102]
-	GetHandleVerifier [0x0x7ff79ce650af+224063]
-	GetHandleVerifier [0x0x7ff79ce4af64+117236]
-	GetHandleVerifier [0x0x7ff79ce4b119+117673]
-	GetHandleVerifier [0x0x7ff79ce310a8+11064]
+	GetHandleVerifier [0x0x7ff716ef1eb5+80197]
+	GetHandleVerifier [0x0x7ff716ef1f10+80288]
+	(No symbol) [0x0x7ff716c702fa]
+	(No symbol) [0x0x7ff716cc7cd7]
+	(No symbol) [0x0x7ff716cc7f9c]
+	(No symbol) [0x0x7ff716d1ba87]
+	(No symbol) [0x0x7ff716cf03bf]
+	(No symbol) [0x0x7ff716d187fb]
+	(No symbol) [0x0x7ff716cf0153]
+	(No symbol) [0x0x7ff716cb8b02]
+	(No symbol) [0x0x7ff716cb98d3]
+	GetHandleVerifier [0x0x7ff7171ae83d+2949837]
+	GetHandleVerifier [0x0x7ff7171a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7171c86c7+3055959]
+	GetHandleVerifier [0x0x7ff716f0cfee+191102]
+	GetHandleVerifier [0x0x7ff716f150af+224063]
+	GetHandleVerifier [0x0x7ff716efaf64+117236]
+	GetHandleVerifier [0x0x7ff716efb119+117673]
+	GetHandleVerifier [0x0x7ff716ee10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1568,25 +1568,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff79ce41eb5+80197]
-	GetHandleVerifier [0x0x7ff79ce41f10+80288]
-	(No symbol) [0x0x7ff79cbc02fa]
-	(No symbol) [0x0x7ff79cc17cd7]
-	(No symbol) [0x0x7ff79cc17f9c]
-	(No symbol) [0x0x7ff79cc6ba87]
-	(No symbol) [0x0x7ff79cc403bf]
-	(No symbol) [0x0x7ff79cc687fb]
-	(No symbol) [0x0x7ff79cc40153]
-	(No symbol) [0x0x7ff79cc08b02]
-	(No symbol) [0x0x7ff79cc098d3]
-	GetHandleVerifier [0x0x7ff79d0fe83d+2949837]
-	GetHandleVerifier [0x0x7ff79d0f8c6a+2926330]
-	GetHandleVerifier [0x0x7ff79d1186c7+3055959]
-	GetHandleVerifier [0x0x7ff79ce5cfee+191102]
-	GetHandleVerifier [0x0x7ff79ce650af+224063]
-	GetHandleVerifier [0x0x7ff79ce4af64+117236]
-	GetHandleVerifier [0x0x7ff79ce4b119+117673]
-	GetHandleVerifier [0x0x7ff79ce310a8+11064]
+	GetHandleVerifier [0x0x7ff716ef1eb5+80197]
+	GetHandleVerifier [0x0x7ff716ef1f10+80288]
+	(No symbol) [0x0x7ff716c702fa]
+	(No symbol) [0x0x7ff716cc7cd7]
+	(No symbol) [0x0x7ff716cc7f9c]
+	(No symbol) [0x0x7ff716d1ba87]
+	(No symbol) [0x0x7ff716cf03bf]
+	(No symbol) [0x0x7ff716d187fb]
+	(No symbol) [0x0x7ff716cf0153]
+	(No symbol) [0x0x7ff716cb8b02]
+	(No symbol) [0x0x7ff716cb98d3]
+	GetHandleVerifier [0x0x7ff7171ae83d+2949837]
+	GetHandleVerifier [0x0x7ff7171a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7171c86c7+3055959]
+	GetHandleVerifier [0x0x7ff716f0cfee+191102]
+	GetHandleVerifier [0x0x7ff716f150af+224063]
+	GetHandleVerifier [0x0x7ff716efaf64+117236]
+	GetHandleVerifier [0x0x7ff716efb119+117673]
+	GetHandleVerifier [0x0x7ff716ee10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1690,25 +1690,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff79ce41eb5+80197]
-	GetHandleVerifier [0x0x7ff79ce41f10+80288]
-	(No symbol) [0x0x7ff79cbc02fa]
-	(No symbol) [0x0x7ff79cc17cd7]
-	(No symbol) [0x0x7ff79cc17f9c]
-	(No symbol) [0x0x7ff79cc6ba87]
-	(No symbol) [0x0x7ff79cc403bf]
-	(No symbol) [0x0x7ff79cc687fb]
-	(No symbol) [0x0x7ff79cc40153]
-	(No symbol) [0x0x7ff79cc08b02]
-	(No symbol) [0x0x7ff79cc098d3]
-	GetHandleVerifier [0x0x7ff79d0fe83d+2949837]
-	GetHandleVerifier [0x0x7ff79d0f8c6a+2926330]
-	GetHandleVerifier [0x0x7ff79d1186c7+3055959]
-	GetHandleVerifier [0x0x7ff79ce5cfee+191102]
-	GetHandleVerifier [0x0x7ff79ce650af+224063]
-	GetHandleVerifier [0x0x7ff79ce4af64+117236]
-	GetHandleVerifier [0x0x7ff79ce4b119+117673]
-	GetHandleVerifier [0x0x7ff79ce310a8+11064]
+	GetHandleVerifier [0x0x7ff716ef1eb5+80197]
+	GetHandleVerifier [0x0x7ff716ef1f10+80288]
+	(No symbol) [0x0x7ff716c702fa]
+	(No symbol) [0x0x7ff716cc7cd7]
+	(No symbol) [0x0x7ff716cc7f9c]
+	(No symbol) [0x0x7ff716d1ba87]
+	(No symbol) [0x0x7ff716cf03bf]
+	(No symbol) [0x0x7ff716d187fb]
+	(No symbol) [0x0x7ff716cf0153]
+	(No symbol) [0x0x7ff716cb8b02]
+	(No symbol) [0x0x7ff716cb98d3]
+	GetHandleVerifier [0x0x7ff7171ae83d+2949837]
+	GetHandleVerifier [0x0x7ff7171a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7171c86c7+3055959]
+	GetHandleVerifier [0x0x7ff716f0cfee+191102]
+	GetHandleVerifier [0x0x7ff716f150af+224063]
+	GetHandleVerifier [0x0x7ff716efaf64+117236]
+	GetHandleVerifier [0x0x7ff716efb119+117673]
+	GetHandleVerifier [0x0x7ff716ee10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1812,25 +1812,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff79ce41eb5+80197]
-	GetHandleVerifier [0x0x7ff79ce41f10+80288]
-	(No symbol) [0x0x7ff79cbc02fa]
-	(No symbol) [0x0x7ff79cc17cd7]
-	(No symbol) [0x0x7ff79cc17f9c]
-	(No symbol) [0x0x7ff79cc6ba87]
-	(No symbol) [0x0x7ff79cc403bf]
-	(No symbol) [0x0x7ff79cc687fb]
-	(No symbol) [0x0x7ff79cc40153]
-	(No symbol) [0x0x7ff79cc08b02]
-	(No symbol) [0x0x7ff79cc098d3]
-	GetHandleVerifier [0x0x7ff79d0fe83d+2949837]
-	GetHandleVerifier [0x0x7ff79d0f8c6a+2926330]
-	GetHandleVerifier [0x0x7ff79d1186c7+3055959]
-	GetHandleVerifier [0x0x7ff79ce5cfee+191102]
-	GetHandleVerifier [0x0x7ff79ce650af+224063]
-	GetHandleVerifier [0x0x7ff79ce4af64+117236]
-	GetHandleVerifier [0x0x7ff79ce4b119+117673]
-	GetHandleVerifier [0x0x7ff79ce310a8+11064]
+	GetHandleVerifier [0x0x7ff716ef1eb5+80197]
+	GetHandleVerifier [0x0x7ff716ef1f10+80288]
+	(No symbol) [0x0x7ff716c702fa]
+	(No symbol) [0x0x7ff716cc7cd7]
+	(No symbol) [0x0x7ff716cc7f9c]
+	(No symbol) [0x0x7ff716d1ba87]
+	(No symbol) [0x0x7ff716cf03bf]
+	(No symbol) [0x0x7ff716d187fb]
+	(No symbol) [0x0x7ff716cf0153]
+	(No symbol) [0x0x7ff716cb8b02]
+	(No symbol) [0x0x7ff716cb98d3]
+	GetHandleVerifier [0x0x7ff7171ae83d+2949837]
+	GetHandleVerifier [0x0x7ff7171a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7171c86c7+3055959]
+	GetHandleVerifier [0x0x7ff716f0cfee+191102]
+	GetHandleVerifier [0x0x7ff716f150af+224063]
+	GetHandleVerifier [0x0x7ff716efaf64+117236]
+	GetHandleVerifier [0x0x7ff716efb119+117673]
+	GetHandleVerifier [0x0x7ff716ee10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1934,25 +1934,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff79ce41eb5+80197]
-	GetHandleVerifier [0x0x7ff79ce41f10+80288]
-	(No symbol) [0x0x7ff79cbc02fa]
-	(No symbol) [0x0x7ff79cc17cd7]
-	(No symbol) [0x0x7ff79cc17f9c]
-	(No symbol) [0x0x7ff79cc6ba87]
-	(No symbol) [0x0x7ff79cc403bf]
-	(No symbol) [0x0x7ff79cc687fb]
-	(No symbol) [0x0x7ff79cc40153]
-	(No symbol) [0x0x7ff79cc08b02]
-	(No symbol) [0x0x7ff79cc098d3]
-	GetHandleVerifier [0x0x7ff79d0fe83d+2949837]
-	GetHandleVerifier [0x0x7ff79d0f8c6a+2926330]
-	GetHandleVerifier [0x0x7ff79d1186c7+3055959]
-	GetHandleVerifier [0x0x7ff79ce5cfee+191102]
-	GetHandleVerifier [0x0x7ff79ce650af+224063]
-	GetHandleVerifier [0x0x7ff79ce4af64+117236]
-	GetHandleVerifier [0x0x7ff79ce4b119+117673]
-	GetHandleVerifier [0x0x7ff79ce310a8+11064]
+	GetHandleVerifier [0x0x7ff716ef1eb5+80197]
+	GetHandleVerifier [0x0x7ff716ef1f10+80288]
+	(No symbol) [0x0x7ff716c702fa]
+	(No symbol) [0x0x7ff716cc7cd7]
+	(No symbol) [0x0x7ff716cc7f9c]
+	(No symbol) [0x0x7ff716d1ba87]
+	(No symbol) [0x0x7ff716cf03bf]
+	(No symbol) [0x0x7ff716d187fb]
+	(No symbol) [0x0x7ff716cf0153]
+	(No symbol) [0x0x7ff716cb8b02]
+	(No symbol) [0x0x7ff716cb98d3]
+	GetHandleVerifier [0x0x7ff7171ae83d+2949837]
+	GetHandleVerifier [0x0x7ff7171a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7171c86c7+3055959]
+	GetHandleVerifier [0x0x7ff716f0cfee+191102]
+	GetHandleVerifier [0x0x7ff716f150af+224063]
+	GetHandleVerifier [0x0x7ff716efaf64+117236]
+	GetHandleVerifier [0x0x7ff716efb119+117673]
+	GetHandleVerifier [0x0x7ff716ee10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2056,25 +2056,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff79ce41eb5+80197]
-	GetHandleVerifier [0x0x7ff79ce41f10+80288]
-	(No symbol) [0x0x7ff79cbc02fa]
-	(No symbol) [0x0x7ff79cc17cd7]
-	(No symbol) [0x0x7ff79cc17f9c]
-	(No symbol) [0x0x7ff79cc6ba87]
-	(No symbol) [0x0x7ff79cc403bf]
-	(No symbol) [0x0x7ff79cc687fb]
-	(No symbol) [0x0x7ff79cc40153]
-	(No symbol) [0x0x7ff79cc08b02]
-	(No symbol) [0x0x7ff79cc098d3]
-	GetHandleVerifier [0x0x7ff79d0fe83d+2949837]
-	GetHandleVerifier [0x0x7ff79d0f8c6a+2926330]
-	GetHandleVerifier [0x0x7ff79d1186c7+3055959]
-	GetHandleVerifier [0x0x7ff79ce5cfee+191102]
-	GetHandleVerifier [0x0x7ff79ce650af+224063]
-	GetHandleVerifier [0x0x7ff79ce4af64+117236]
-	GetHandleVerifier [0x0x7ff79ce4b119+117673]
-	GetHandleVerifier [0x0x7ff79ce310a8+11064]
+	GetHandleVerifier [0x0x7ff716ef1eb5+80197]
+	GetHandleVerifier [0x0x7ff716ef1f10+80288]
+	(No symbol) [0x0x7ff716c702fa]
+	(No symbol) [0x0x7ff716cc7cd7]
+	(No symbol) [0x0x7ff716cc7f9c]
+	(No symbol) [0x0x7ff716d1ba87]
+	(No symbol) [0x0x7ff716cf03bf]
+	(No symbol) [0x0x7ff716d187fb]
+	(No symbol) [0x0x7ff716cf0153]
+	(No symbol) [0x0x7ff716cb8b02]
+	(No symbol) [0x0x7ff716cb98d3]
+	GetHandleVerifier [0x0x7ff7171ae83d+2949837]
+	GetHandleVerifier [0x0x7ff7171a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7171c86c7+3055959]
+	GetHandleVerifier [0x0x7ff716f0cfee+191102]
+	GetHandleVerifier [0x0x7ff716f150af+224063]
+	GetHandleVerifier [0x0x7ff716efaf64+117236]
+	GetHandleVerifier [0x0x7ff716efb119+117673]
+	GetHandleVerifier [0x0x7ff716ee10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2177,25 +2177,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff79ce41eb5+80197]
-	GetHandleVerifier [0x0x7ff79ce41f10+80288]
-	(No symbol) [0x0x7ff79cbc02fa]
-	(No symbol) [0x0x7ff79cc17cd7]
-	(No symbol) [0x0x7ff79cc17f9c]
-	(No symbol) [0x0x7ff79cc6ba87]
-	(No symbol) [0x0x7ff79cc403bf]
-	(No symbol) [0x0x7ff79cc687fb]
-	(No symbol) [0x0x7ff79cc40153]
-	(No symbol) [0x0x7ff79cc08b02]
-	(No symbol) [0x0x7ff79cc098d3]
-	GetHandleVerifier [0x0x7ff79d0fe83d+2949837]
-	GetHandleVerifier [0x0x7ff79d0f8c6a+2926330]
-	GetHandleVerifier [0x0x7ff79d1186c7+3055959]
-	GetHandleVerifier [0x0x7ff79ce5cfee+191102]
-	GetHandleVerifier [0x0x7ff79ce650af+224063]
-	GetHandleVerifier [0x0x7ff79ce4af64+117236]
-	GetHandleVerifier [0x0x7ff79ce4b119+117673]
-	GetHandleVerifier [0x0x7ff79ce310a8+11064]
+	GetHandleVerifier [0x0x7ff716ef1eb5+80197]
+	GetHandleVerifier [0x0x7ff716ef1f10+80288]
+	(No symbol) [0x0x7ff716c702fa]
+	(No symbol) [0x0x7ff716cc7cd7]
+	(No symbol) [0x0x7ff716cc7f9c]
+	(No symbol) [0x0x7ff716d1ba87]
+	(No symbol) [0x0x7ff716cf03bf]
+	(No symbol) [0x0x7ff716d187fb]
+	(No symbol) [0x0x7ff716cf0153]
+	(No symbol) [0x0x7ff716cb8b02]
+	(No symbol) [0x0x7ff716cb98d3]
+	GetHandleVerifier [0x0x7ff7171ae83d+2949837]
+	GetHandleVerifier [0x0x7ff7171a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7171c86c7+3055959]
+	GetHandleVerifier [0x0x7ff716f0cfee+191102]
+	GetHandleVerifier [0x0x7ff716f150af+224063]
+	GetHandleVerifier [0x0x7ff716efaf64+117236]
+	GetHandleVerifier [0x0x7ff716efb119+117673]
+	GetHandleVerifier [0x0x7ff716ee10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2299,25 +2299,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff79ce41eb5+80197]
-	GetHandleVerifier [0x0x7ff79ce41f10+80288]
-	(No symbol) [0x0x7ff79cbc02fa]
-	(No symbol) [0x0x7ff79cc17cd7]
-	(No symbol) [0x0x7ff79cc17f9c]
-	(No symbol) [0x0x7ff79cc6ba87]
-	(No symbol) [0x0x7ff79cc403bf]
-	(No symbol) [0x0x7ff79cc687fb]
-	(No symbol) [0x0x7ff79cc40153]
-	(No symbol) [0x0x7ff79cc08b02]
-	(No symbol) [0x0x7ff79cc098d3]
-	GetHandleVerifier [0x0x7ff79d0fe83d+2949837]
-	GetHandleVerifier [0x0x7ff79d0f8c6a+2926330]
-	GetHandleVerifier [0x0x7ff79d1186c7+3055959]
-	GetHandleVerifier [0x0x7ff79ce5cfee+191102]
-	GetHandleVerifier [0x0x7ff79ce650af+224063]
-	GetHandleVerifier [0x0x7ff79ce4af64+117236]
-	GetHandleVerifier [0x0x7ff79ce4b119+117673]
-	GetHandleVerifier [0x0x7ff79ce310a8+11064]
+	GetHandleVerifier [0x0x7ff716ef1eb5+80197]
+	GetHandleVerifier [0x0x7ff716ef1f10+80288]
+	(No symbol) [0x0x7ff716c702fa]
+	(No symbol) [0x0x7ff716cc7cd7]
+	(No symbol) [0x0x7ff716cc7f9c]
+	(No symbol) [0x0x7ff716d1ba87]
+	(No symbol) [0x0x7ff716cf03bf]
+	(No symbol) [0x0x7ff716d187fb]
+	(No symbol) [0x0x7ff716cf0153]
+	(No symbol) [0x0x7ff716cb8b02]
+	(No symbol) [0x0x7ff716cb98d3]
+	GetHandleVerifier [0x0x7ff7171ae83d+2949837]
+	GetHandleVerifier [0x0x7ff7171a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7171c86c7+3055959]
+	GetHandleVerifier [0x0x7ff716f0cfee+191102]
+	GetHandleVerifier [0x0x7ff716f150af+224063]
+	GetHandleVerifier [0x0x7ff716efaf64+117236]
+	GetHandleVerifier [0x0x7ff716efb119+117673]
+	GetHandleVerifier [0x0x7ff716ee10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2519,25 +2519,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff79ce41eb5+80197]
-	GetHandleVerifier [0x0x7ff79ce41f10+80288]
-	(No symbol) [0x0x7ff79cbc02fa]
-	(No symbol) [0x0x7ff79cc17cd7]
-	(No symbol) [0x0x7ff79cc17f9c]
-	(No symbol) [0x0x7ff79cc6ba87]
-	(No symbol) [0x0x7ff79cc403bf]
-	(No symbol) [0x0x7ff79cc687fb]
-	(No symbol) [0x0x7ff79cc40153]
-	(No symbol) [0x0x7ff79cc08b02]
-	(No symbol) [0x0x7ff79cc098d3]
-	GetHandleVerifier [0x0x7ff79d0fe83d+2949837]
-	GetHandleVerifier [0x0x7ff79d0f8c6a+2926330]
-	GetHandleVerifier [0x0x7ff79d1186c7+3055959]
-	GetHandleVerifier [0x0x7ff79ce5cfee+191102]
-	GetHandleVerifier [0x0x7ff79ce650af+224063]
-	GetHandleVerifier [0x0x7ff79ce4af64+117236]
-	GetHandleVerifier [0x0x7ff79ce4b119+117673]
-	GetHandleVerifier [0x0x7ff79ce310a8+11064]
+	GetHandleVerifier [0x0x7ff716ef1eb5+80197]
+	GetHandleVerifier [0x0x7ff716ef1f10+80288]
+	(No symbol) [0x0x7ff716c702fa]
+	(No symbol) [0x0x7ff716cc7cd7]
+	(No symbol) [0x0x7ff716cc7f9c]
+	(No symbol) [0x0x7ff716d1ba87]
+	(No symbol) [0x0x7ff716cf03bf]
+	(No symbol) [0x0x7ff716d187fb]
+	(No symbol) [0x0x7ff716cf0153]
+	(No symbol) [0x0x7ff716cb8b02]
+	(No symbol) [0x0x7ff716cb98d3]
+	GetHandleVerifier [0x0x7ff7171ae83d+2949837]
+	GetHandleVerifier [0x0x7ff7171a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7171c86c7+3055959]
+	GetHandleVerifier [0x0x7ff716f0cfee+191102]
+	GetHandleVerifier [0x0x7ff716f150af+224063]
+	GetHandleVerifier [0x0x7ff716efaf64+117236]
+	GetHandleVerifier [0x0x7ff716efb119+117673]
+	GetHandleVerifier [0x0x7ff716ee10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2640,25 +2640,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff79ce41eb5+80197]
-	GetHandleVerifier [0x0x7ff79ce41f10+80288]
-	(No symbol) [0x0x7ff79cbc02fa]
-	(No symbol) [0x0x7ff79cc17cd7]
-	(No symbol) [0x0x7ff79cc17f9c]
-	(No symbol) [0x0x7ff79cc6ba87]
-	(No symbol) [0x0x7ff79cc403bf]
-	(No symbol) [0x0x7ff79cc687fb]
-	(No symbol) [0x0x7ff79cc40153]
-	(No symbol) [0x0x7ff79cc08b02]
-	(No symbol) [0x0x7ff79cc098d3]
-	GetHandleVerifier [0x0x7ff79d0fe83d+2949837]
-	GetHandleVerifier [0x0x7ff79d0f8c6a+2926330]
-	GetHandleVerifier [0x0x7ff79d1186c7+3055959]
-	GetHandleVerifier [0x0x7ff79ce5cfee+191102]
-	GetHandleVerifier [0x0x7ff79ce650af+224063]
-	GetHandleVerifier [0x0x7ff79ce4af64+117236]
-	GetHandleVerifier [0x0x7ff79ce4b119+117673]
-	GetHandleVerifier [0x0x7ff79ce310a8+11064]
+	GetHandleVerifier [0x0x7ff716ef1eb5+80197]
+	GetHandleVerifier [0x0x7ff716ef1f10+80288]
+	(No symbol) [0x0x7ff716c702fa]
+	(No symbol) [0x0x7ff716cc7cd7]
+	(No symbol) [0x0x7ff716cc7f9c]
+	(No symbol) [0x0x7ff716d1ba87]
+	(No symbol) [0x0x7ff716cf03bf]
+	(No symbol) [0x0x7ff716d187fb]
+	(No symbol) [0x0x7ff716cf0153]
+	(No symbol) [0x0x7ff716cb8b02]
+	(No symbol) [0x0x7ff716cb98d3]
+	GetHandleVerifier [0x0x7ff7171ae83d+2949837]
+	GetHandleVerifier [0x0x7ff7171a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7171c86c7+3055959]
+	GetHandleVerifier [0x0x7ff716f0cfee+191102]
+	GetHandleVerifier [0x0x7ff716f150af+224063]
+	GetHandleVerifier [0x0x7ff716efaf64+117236]
+	GetHandleVerifier [0x0x7ff716efb119+117673]
+	GetHandleVerifier [0x0x7ff716ee10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2761,25 +2761,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff79ce41eb5+80197]
-	GetHandleVerifier [0x0x7ff79ce41f10+80288]
-	(No symbol) [0x0x7ff79cbc02fa]
-	(No symbol) [0x0x7ff79cc17cd7]
-	(No symbol) [0x0x7ff79cc17f9c]
-	(No symbol) [0x0x7ff79cc6ba87]
-	(No symbol) [0x0x7ff79cc403bf]
-	(No symbol) [0x0x7ff79cc687fb]
-	(No symbol) [0x0x7ff79cc40153]
-	(No symbol) [0x0x7ff79cc08b02]
-	(No symbol) [0x0x7ff79cc098d3]
-	GetHandleVerifier [0x0x7ff79d0fe83d+2949837]
-	GetHandleVerifier [0x0x7ff79d0f8c6a+2926330]
-	GetHandleVerifier [0x0x7ff79d1186c7+3055959]
-	GetHandleVerifier [0x0x7ff79ce5cfee+191102]
-	GetHandleVerifier [0x0x7ff79ce650af+224063]
-	GetHandleVerifier [0x0x7ff79ce4af64+117236]
-	GetHandleVerifier [0x0x7ff79ce4b119+117673]
-	GetHandleVerifier [0x0x7ff79ce310a8+11064]
+	GetHandleVerifier [0x0x7ff716ef1eb5+80197]
+	GetHandleVerifier [0x0x7ff716ef1f10+80288]
+	(No symbol) [0x0x7ff716c702fa]
+	(No symbol) [0x0x7ff716cc7cd7]
+	(No symbol) [0x0x7ff716cc7f9c]
+	(No symbol) [0x0x7ff716d1ba87]
+	(No symbol) [0x0x7ff716cf03bf]
+	(No symbol) [0x0x7ff716d187fb]
+	(No symbol) [0x0x7ff716cf0153]
+	(No symbol) [0x0x7ff716cb8b02]
+	(No symbol) [0x0x7ff716cb98d3]
+	GetHandleVerifier [0x0x7ff7171ae83d+2949837]
+	GetHandleVerifier [0x0x7ff7171a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7171c86c7+3055959]
+	GetHandleVerifier [0x0x7ff716f0cfee+191102]
+	GetHandleVerifier [0x0x7ff716f150af+224063]
+	GetHandleVerifier [0x0x7ff716efaf64+117236]
+	GetHandleVerifier [0x0x7ff716efb119+117673]
+	GetHandleVerifier [0x0x7ff716ee10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2882,25 +2882,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff79ce41eb5+80197]
-	GetHandleVerifier [0x0x7ff79ce41f10+80288]
-	(No symbol) [0x0x7ff79cbc02fa]
-	(No symbol) [0x0x7ff79cc17cd7]
-	(No symbol) [0x0x7ff79cc17f9c]
-	(No symbol) [0x0x7ff79cc6ba87]
-	(No symbol) [0x0x7ff79cc403bf]
-	(No symbol) [0x0x7ff79cc687fb]
-	(No symbol) [0x0x7ff79cc40153]
-	(No symbol) [0x0x7ff79cc08b02]
-	(No symbol) [0x0x7ff79cc098d3]
-	GetHandleVerifier [0x0x7ff79d0fe83d+2949837]
-	GetHandleVerifier [0x0x7ff79d0f8c6a+2926330]
-	GetHandleVerifier [0x0x7ff79d1186c7+3055959]
-	GetHandleVerifier [0x0x7ff79ce5cfee+191102]
-	GetHandleVerifier [0x0x7ff79ce650af+224063]
-	GetHandleVerifier [0x0x7ff79ce4af64+117236]
-	GetHandleVerifier [0x0x7ff79ce4b119+117673]
-	GetHandleVerifier [0x0x7ff79ce310a8+11064]
+	GetHandleVerifier [0x0x7ff716ef1eb5+80197]
+	GetHandleVerifier [0x0x7ff716ef1f10+80288]
+	(No symbol) [0x0x7ff716c702fa]
+	(No symbol) [0x0x7ff716cc7cd7]
+	(No symbol) [0x0x7ff716cc7f9c]
+	(No symbol) [0x0x7ff716d1ba87]
+	(No symbol) [0x0x7ff716cf03bf]
+	(No symbol) [0x0x7ff716d187fb]
+	(No symbol) [0x0x7ff716cf0153]
+	(No symbol) [0x0x7ff716cb8b02]
+	(No symbol) [0x0x7ff716cb98d3]
+	GetHandleVerifier [0x0x7ff7171ae83d+2949837]
+	GetHandleVerifier [0x0x7ff7171a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7171c86c7+3055959]
+	GetHandleVerifier [0x0x7ff716f0cfee+191102]
+	GetHandleVerifier [0x0x7ff716f150af+224063]
+	GetHandleVerifier [0x0x7ff716efaf64+117236]
+	GetHandleVerifier [0x0x7ff716efb119+117673]
+	GetHandleVerifier [0x0x7ff716ee10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3003,25 +3003,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff79ce41eb5+80197]
-	GetHandleVerifier [0x0x7ff79ce41f10+80288]
-	(No symbol) [0x0x7ff79cbc02fa]
-	(No symbol) [0x0x7ff79cc17cd7]
-	(No symbol) [0x0x7ff79cc17f9c]
-	(No symbol) [0x0x7ff79cc6ba87]
-	(No symbol) [0x0x7ff79cc403bf]
-	(No symbol) [0x0x7ff79cc687fb]
-	(No symbol) [0x0x7ff79cc40153]
-	(No symbol) [0x0x7ff79cc08b02]
-	(No symbol) [0x0x7ff79cc098d3]
-	GetHandleVerifier [0x0x7ff79d0fe83d+2949837]
-	GetHandleVerifier [0x0x7ff79d0f8c6a+2926330]
-	GetHandleVerifier [0x0x7ff79d1186c7+3055959]
-	GetHandleVerifier [0x0x7ff79ce5cfee+191102]
-	GetHandleVerifier [0x0x7ff79ce650af+224063]
-	GetHandleVerifier [0x0x7ff79ce4af64+117236]
-	GetHandleVerifier [0x0x7ff79ce4b119+117673]
-	GetHandleVerifier [0x0x7ff79ce310a8+11064]
+	GetHandleVerifier [0x0x7ff716ef1eb5+80197]
+	GetHandleVerifier [0x0x7ff716ef1f10+80288]
+	(No symbol) [0x0x7ff716c702fa]
+	(No symbol) [0x0x7ff716cc7cd7]
+	(No symbol) [0x0x7ff716cc7f9c]
+	(No symbol) [0x0x7ff716d1ba87]
+	(No symbol) [0x0x7ff716cf03bf]
+	(No symbol) [0x0x7ff716d187fb]
+	(No symbol) [0x0x7ff716cf0153]
+	(No symbol) [0x0x7ff716cb8b02]
+	(No symbol) [0x0x7ff716cb98d3]
+	GetHandleVerifier [0x0x7ff7171ae83d+2949837]
+	GetHandleVerifier [0x0x7ff7171a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7171c86c7+3055959]
+	GetHandleVerifier [0x0x7ff716f0cfee+191102]
+	GetHandleVerifier [0x0x7ff716f150af+224063]
+	GetHandleVerifier [0x0x7ff716efaf64+117236]
+	GetHandleVerifier [0x0x7ff716efb119+117673]
+	GetHandleVerifier [0x0x7ff716ee10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3124,25 +3124,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff79ce41eb5+80197]
-	GetHandleVerifier [0x0x7ff79ce41f10+80288]
-	(No symbol) [0x0x7ff79cbc02fa]
-	(No symbol) [0x0x7ff79cc17cd7]
-	(No symbol) [0x0x7ff79cc17f9c]
-	(No symbol) [0x0x7ff79cc6ba87]
-	(No symbol) [0x0x7ff79cc403bf]
-	(No symbol) [0x0x7ff79cc687fb]
-	(No symbol) [0x0x7ff79cc40153]
-	(No symbol) [0x0x7ff79cc08b02]
-	(No symbol) [0x0x7ff79cc098d3]
-	GetHandleVerifier [0x0x7ff79d0fe83d+2949837]
-	GetHandleVerifier [0x0x7ff79d0f8c6a+2926330]
-	GetHandleVerifier [0x0x7ff79d1186c7+3055959]
-	GetHandleVerifier [0x0x7ff79ce5cfee+191102]
-	GetHandleVerifier [0x0x7ff79ce650af+224063]
-	GetHandleVerifier [0x0x7ff79ce4af64+117236]
-	GetHandleVerifier [0x0x7ff79ce4b119+117673]
-	GetHandleVerifier [0x0x7ff79ce310a8+11064]
+	GetHandleVerifier [0x0x7ff716ef1eb5+80197]
+	GetHandleVerifier [0x0x7ff716ef1f10+80288]
+	(No symbol) [0x0x7ff716c702fa]
+	(No symbol) [0x0x7ff716cc7cd7]
+	(No symbol) [0x0x7ff716cc7f9c]
+	(No symbol) [0x0x7ff716d1ba87]
+	(No symbol) [0x0x7ff716cf03bf]
+	(No symbol) [0x0x7ff716d187fb]
+	(No symbol) [0x0x7ff716cf0153]
+	(No symbol) [0x0x7ff716cb8b02]
+	(No symbol) [0x0x7ff716cb98d3]
+	GetHandleVerifier [0x0x7ff7171ae83d+2949837]
+	GetHandleVerifier [0x0x7ff7171a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7171c86c7+3055959]
+	GetHandleVerifier [0x0x7ff716f0cfee+191102]
+	GetHandleVerifier [0x0x7ff716f150af+224063]
+	GetHandleVerifier [0x0x7ff716efaf64+117236]
+	GetHandleVerifier [0x0x7ff716efb119+117673]
+	GetHandleVerifier [0x0x7ff716ee10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3245,25 +3245,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff79ce41eb5+80197]
-	GetHandleVerifier [0x0x7ff79ce41f10+80288]
-	(No symbol) [0x0x7ff79cbc02fa]
-	(No symbol) [0x0x7ff79cc17cd7]
-	(No symbol) [0x0x7ff79cc17f9c]
-	(No symbol) [0x0x7ff79cc6ba87]
-	(No symbol) [0x0x7ff79cc403bf]
-	(No symbol) [0x0x7ff79cc687fb]
-	(No symbol) [0x0x7ff79cc40153]
-	(No symbol) [0x0x7ff79cc08b02]
-	(No symbol) [0x0x7ff79cc098d3]
-	GetHandleVerifier [0x0x7ff79d0fe83d+2949837]
-	GetHandleVerifier [0x0x7ff79d0f8c6a+2926330]
-	GetHandleVerifier [0x0x7ff79d1186c7+3055959]
-	GetHandleVerifier [0x0x7ff79ce5cfee+191102]
-	GetHandleVerifier [0x0x7ff79ce650af+224063]
-	GetHandleVerifier [0x0x7ff79ce4af64+117236]
-	GetHandleVerifier [0x0x7ff79ce4b119+117673]
-	GetHandleVerifier [0x0x7ff79ce310a8+11064]
+	GetHandleVerifier [0x0x7ff716ef1eb5+80197]
+	GetHandleVerifier [0x0x7ff716ef1f10+80288]
+	(No symbol) [0x0x7ff716c702fa]
+	(No symbol) [0x0x7ff716cc7cd7]
+	(No symbol) [0x0x7ff716cc7f9c]
+	(No symbol) [0x0x7ff716d1ba87]
+	(No symbol) [0x0x7ff716cf03bf]
+	(No symbol) [0x0x7ff716d187fb]
+	(No symbol) [0x0x7ff716cf0153]
+	(No symbol) [0x0x7ff716cb8b02]
+	(No symbol) [0x0x7ff716cb98d3]
+	GetHandleVerifier [0x0x7ff7171ae83d+2949837]
+	GetHandleVerifier [0x0x7ff7171a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7171c86c7+3055959]
+	GetHandleVerifier [0x0x7ff716f0cfee+191102]
+	GetHandleVerifier [0x0x7ff716f150af+224063]
+	GetHandleVerifier [0x0x7ff716efaf64+117236]
+	GetHandleVerifier [0x0x7ff716efb119+117673]
+	GetHandleVerifier [0x0x7ff716ee10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3366,25 +3366,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff79ce41eb5+80197]
-	GetHandleVerifier [0x0x7ff79ce41f10+80288]
-	(No symbol) [0x0x7ff79cbc02fa]
-	(No symbol) [0x0x7ff79cc17cd7]
-	(No symbol) [0x0x7ff79cc17f9c]
-	(No symbol) [0x0x7ff79cc6ba87]
-	(No symbol) [0x0x7ff79cc403bf]
-	(No symbol) [0x0x7ff79cc687fb]
-	(No symbol) [0x0x7ff79cc40153]
-	(No symbol) [0x0x7ff79cc08b02]
-	(No symbol) [0x0x7ff79cc098d3]
-	GetHandleVerifier [0x0x7ff79d0fe83d+2949837]
-	GetHandleVerifier [0x0x7ff79d0f8c6a+2926330]
-	GetHandleVerifier [0x0x7ff79d1186c7+3055959]
-	GetHandleVerifier [0x0x7ff79ce5cfee+191102]
-	GetHandleVerifier [0x0x7ff79ce650af+224063]
-	GetHandleVerifier [0x0x7ff79ce4af64+117236]
-	GetHandleVerifier [0x0x7ff79ce4b119+117673]
-	GetHandleVerifier [0x0x7ff79ce310a8+11064]
+	GetHandleVerifier [0x0x7ff716ef1eb5+80197]
+	GetHandleVerifier [0x0x7ff716ef1f10+80288]
+	(No symbol) [0x0x7ff716c702fa]
+	(No symbol) [0x0x7ff716cc7cd7]
+	(No symbol) [0x0x7ff716cc7f9c]
+	(No symbol) [0x0x7ff716d1ba87]
+	(No symbol) [0x0x7ff716cf03bf]
+	(No symbol) [0x0x7ff716d187fb]
+	(No symbol) [0x0x7ff716cf0153]
+	(No symbol) [0x0x7ff716cb8b02]
+	(No symbol) [0x0x7ff716cb98d3]
+	GetHandleVerifier [0x0x7ff7171ae83d+2949837]
+	GetHandleVerifier [0x0x7ff7171a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7171c86c7+3055959]
+	GetHandleVerifier [0x0x7ff716f0cfee+191102]
+	GetHandleVerifier [0x0x7ff716f150af+224063]
+	GetHandleVerifier [0x0x7ff716efaf64+117236]
+	GetHandleVerifier [0x0x7ff716efb119+117673]
+	GetHandleVerifier [0x0x7ff716ee10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3487,25 +3487,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff79ce41eb5+80197]
-	GetHandleVerifier [0x0x7ff79ce41f10+80288]
-	(No symbol) [0x0x7ff79cbc02fa]
-	(No symbol) [0x0x7ff79cc17cd7]
-	(No symbol) [0x0x7ff79cc17f9c]
-	(No symbol) [0x0x7ff79cc6ba87]
-	(No symbol) [0x0x7ff79cc403bf]
-	(No symbol) [0x0x7ff79cc687fb]
-	(No symbol) [0x0x7ff79cc40153]
-	(No symbol) [0x0x7ff79cc08b02]
-	(No symbol) [0x0x7ff79cc098d3]
-	GetHandleVerifier [0x0x7ff79d0fe83d+2949837]
-	GetHandleVerifier [0x0x7ff79d0f8c6a+2926330]
-	GetHandleVerifier [0x0x7ff79d1186c7+3055959]
-	GetHandleVerifier [0x0x7ff79ce5cfee+191102]
-	GetHandleVerifier [0x0x7ff79ce650af+224063]
-	GetHandleVerifier [0x0x7ff79ce4af64+117236]
-	GetHandleVerifier [0x0x7ff79ce4b119+117673]
-	GetHandleVerifier [0x0x7ff79ce310a8+11064]
+	GetHandleVerifier [0x0x7ff716ef1eb5+80197]
+	GetHandleVerifier [0x0x7ff716ef1f10+80288]
+	(No symbol) [0x0x7ff716c702fa]
+	(No symbol) [0x0x7ff716cc7cd7]
+	(No symbol) [0x0x7ff716cc7f9c]
+	(No symbol) [0x0x7ff716d1ba87]
+	(No symbol) [0x0x7ff716cf03bf]
+	(No symbol) [0x0x7ff716d187fb]
+	(No symbol) [0x0x7ff716cf0153]
+	(No symbol) [0x0x7ff716cb8b02]
+	(No symbol) [0x0x7ff716cb98d3]
+	GetHandleVerifier [0x0x7ff7171ae83d+2949837]
+	GetHandleVerifier [0x0x7ff7171a8c6a+2926330]
+	GetHandleVerifier [0x0x7ff7171c86c7+3055959]
+	GetHandleVerifier [0x0x7ff716f0cfee+191102]
+	GetHandleVerifier [0x0x7ff716f150af+224063]
+	GetHandleVerifier [0x0x7ff716efaf64+117236]
+	GetHandleVerifier [0x0x7ff716efb119+117673]
+	GetHandleVerifier [0x0x7ff716ee10a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
